--- a/artfynd/S 2068-2026 artfynd.xlsx
+++ b/artfynd/S 2068-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277955</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277935</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277940</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277945</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277947</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277948</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277950</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277954</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277957</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277942</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277943</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277941</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277949</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2226,6 +2296,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277953</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2337,6 +2412,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277956</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2448,6 +2528,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277939</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2559,6 +2644,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277944</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277932</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277937</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2892,6 +2992,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277946</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3003,6 +3108,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277958</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3114,8 +3224,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277933</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2068-2026 artfynd.xlsx
+++ b/artfynd/S 2068-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135648264</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135648413</v>
       </c>
       <c r="B3" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135648414</v>
       </c>
       <c r="B4" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135648421</v>
       </c>
       <c r="B5" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135648430</v>
       </c>
       <c r="B6" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135648435</v>
       </c>
       <c r="B7" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135648312</v>
       </c>
       <c r="B12" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135648365</v>
       </c>
       <c r="B13" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135648246</v>
       </c>
       <c r="B14" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135648255</v>
       </c>
       <c r="B15" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135648260</v>
       </c>
       <c r="B16" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135648276</v>
       </c>
       <c r="B17" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135648278</v>
       </c>
       <c r="B18" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135648281</v>
       </c>
       <c r="B19" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135648283</v>
       </c>
       <c r="B20" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135648284</v>
       </c>
       <c r="B21" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135648288</v>
       </c>
       <c r="B22" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135648298</v>
       </c>
       <c r="B23" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135648304</v>
       </c>
       <c r="B24" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135648305</v>
       </c>
       <c r="B25" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135648335</v>
       </c>
       <c r="B26" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135648338</v>
       </c>
       <c r="B27" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135648340</v>
       </c>
       <c r="B28" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135648341</v>
       </c>
       <c r="B29" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135648344</v>
       </c>
       <c r="B30" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>135648345</v>
       </c>
       <c r="B31" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>135648347</v>
       </c>
       <c r="B32" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135648348</v>
       </c>
       <c r="B33" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135648351</v>
       </c>
       <c r="B34" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135648354</v>
       </c>
       <c r="B35" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135648356</v>
       </c>
       <c r="B36" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135648357</v>
       </c>
       <c r="B37" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135648370</v>
       </c>
       <c r="B38" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>135648372</v>
       </c>
       <c r="B39" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135648398</v>
       </c>
       <c r="B40" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135648411</v>
       </c>
       <c r="B41" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135648415</v>
       </c>
       <c r="B42" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135648418</v>
       </c>
       <c r="B43" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135648419</v>
       </c>
       <c r="B44" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135648420</v>
       </c>
       <c r="B45" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>135648423</v>
       </c>
       <c r="B46" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>135648425</v>
       </c>
       <c r="B47" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135648429</v>
       </c>
       <c r="B48" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>135648432</v>
       </c>
       <c r="B49" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>135648433</v>
       </c>
       <c r="B50" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135648436</v>
       </c>
       <c r="B51" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>135648437</v>
       </c>
       <c r="B52" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>135648440</v>
       </c>
       <c r="B53" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135648342</v>
       </c>
       <c r="B54" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>135648256</v>
       </c>
       <c r="B58" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135648263</v>
       </c>
       <c r="B59" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135648275</v>
       </c>
       <c r="B60" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>135648282</v>
       </c>
       <c r="B61" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>135648285</v>
       </c>
       <c r="B62" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>135648289</v>
       </c>
       <c r="B63" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>135648311</v>
       </c>
       <c r="B64" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>135648353</v>
       </c>
       <c r="B65" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>135648373</v>
       </c>
       <c r="B66" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>135648378</v>
       </c>
       <c r="B67" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>135648389</v>
       </c>
       <c r="B68" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135648397</v>
       </c>
       <c r="B69" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>135648424</v>
       </c>
       <c r="B70" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>135648375</v>
       </c>
       <c r="B71" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>135648426</v>
       </c>
       <c r="B72" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135648427</v>
       </c>
       <c r="B73" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>135648291</v>
       </c>
       <c r="B74" t="n">
-        <v>92059</v>
+        <v>92061</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>135648286</v>
       </c>
       <c r="B75" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>135648431</v>
       </c>
       <c r="B85" t="n">
-        <v>92721</v>
+        <v>92723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>135648302</v>
       </c>
       <c r="B86" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>135648337</v>
       </c>
       <c r="B87" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135648252</v>
       </c>
       <c r="B88" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>135648324</v>
       </c>
       <c r="B172" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>135648374</v>
       </c>
       <c r="B173" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>135648408</v>
       </c>
       <c r="B174" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>135648292</v>
       </c>
       <c r="B175" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>135648396</v>
       </c>
       <c r="B176" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>135648272</v>
       </c>
       <c r="B177" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>135648287</v>
       </c>
       <c r="B178" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>135648314</v>
       </c>
       <c r="B179" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>135648320</v>
       </c>
       <c r="B180" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>135648384</v>
       </c>
       <c r="B181" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>135648394</v>
       </c>
       <c r="B182" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>135648399</v>
       </c>
       <c r="B183" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>135648400</v>
       </c>
       <c r="B184" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>135648401</v>
       </c>
       <c r="B185" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135648404</v>
       </c>
       <c r="B186" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>135648405</v>
       </c>
       <c r="B187" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>135648407</v>
       </c>
       <c r="B188" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>135648258</v>
       </c>
       <c r="B189" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/S 2068-2026 artfynd.xlsx
+++ b/artfynd/S 2068-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135648264</v>
       </c>
       <c r="B2" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135648413</v>
       </c>
       <c r="B3" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135648414</v>
       </c>
       <c r="B4" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135648421</v>
       </c>
       <c r="B5" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135648430</v>
       </c>
       <c r="B6" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135648435</v>
       </c>
       <c r="B7" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>135648367</v>
       </c>
       <c r="B9" t="n">
-        <v>83413</v>
+        <v>83415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135648249</v>
       </c>
       <c r="B10" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135648369</v>
       </c>
       <c r="B11" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135648312</v>
       </c>
       <c r="B12" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135648365</v>
       </c>
       <c r="B13" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135648246</v>
       </c>
       <c r="B14" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135648255</v>
       </c>
       <c r="B15" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135648260</v>
       </c>
       <c r="B16" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135648276</v>
       </c>
       <c r="B17" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135648278</v>
       </c>
       <c r="B18" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135648281</v>
       </c>
       <c r="B19" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135648283</v>
       </c>
       <c r="B20" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135648284</v>
       </c>
       <c r="B21" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135648288</v>
       </c>
       <c r="B22" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135648298</v>
       </c>
       <c r="B23" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135648304</v>
       </c>
       <c r="B24" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135648305</v>
       </c>
       <c r="B25" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135648335</v>
       </c>
       <c r="B26" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135648338</v>
       </c>
       <c r="B27" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135648340</v>
       </c>
       <c r="B28" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135648341</v>
       </c>
       <c r="B29" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135648344</v>
       </c>
       <c r="B30" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>135648345</v>
       </c>
       <c r="B31" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>135648347</v>
       </c>
       <c r="B32" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135648348</v>
       </c>
       <c r="B33" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135648351</v>
       </c>
       <c r="B34" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135648354</v>
       </c>
       <c r="B35" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135648356</v>
       </c>
       <c r="B36" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135648357</v>
       </c>
       <c r="B37" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135648370</v>
       </c>
       <c r="B38" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>135648372</v>
       </c>
       <c r="B39" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135648398</v>
       </c>
       <c r="B40" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135648411</v>
       </c>
       <c r="B41" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135648415</v>
       </c>
       <c r="B42" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135648418</v>
       </c>
       <c r="B43" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135648419</v>
       </c>
       <c r="B44" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135648420</v>
       </c>
       <c r="B45" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>135648423</v>
       </c>
       <c r="B46" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>135648425</v>
       </c>
       <c r="B47" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135648429</v>
       </c>
       <c r="B48" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>135648432</v>
       </c>
       <c r="B49" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>135648433</v>
       </c>
       <c r="B50" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135648436</v>
       </c>
       <c r="B51" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>135648437</v>
       </c>
       <c r="B52" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>135648440</v>
       </c>
       <c r="B53" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135648342</v>
       </c>
       <c r="B54" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>135648256</v>
       </c>
       <c r="B58" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135648263</v>
       </c>
       <c r="B59" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135648275</v>
       </c>
       <c r="B60" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>135648282</v>
       </c>
       <c r="B61" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>135648285</v>
       </c>
       <c r="B62" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>135648289</v>
       </c>
       <c r="B63" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>135648311</v>
       </c>
       <c r="B64" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>135648353</v>
       </c>
       <c r="B65" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>135648373</v>
       </c>
       <c r="B66" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>135648378</v>
       </c>
       <c r="B67" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>135648389</v>
       </c>
       <c r="B68" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135648397</v>
       </c>
       <c r="B69" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>135648424</v>
       </c>
       <c r="B70" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>135648375</v>
       </c>
       <c r="B71" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>135648426</v>
       </c>
       <c r="B72" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135648427</v>
       </c>
       <c r="B73" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>135648291</v>
       </c>
       <c r="B74" t="n">
-        <v>92061</v>
+        <v>92075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>135648286</v>
       </c>
       <c r="B75" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>135648250</v>
       </c>
       <c r="B81" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135648261</v>
       </c>
       <c r="B82" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>135648382</v>
       </c>
       <c r="B83" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>135648393</v>
       </c>
       <c r="B84" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>135648431</v>
       </c>
       <c r="B85" t="n">
-        <v>92723</v>
+        <v>92738</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>135648302</v>
       </c>
       <c r="B86" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>135648337</v>
       </c>
       <c r="B87" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135648252</v>
       </c>
       <c r="B88" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>135648241</v>
       </c>
       <c r="B94" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>135648245</v>
       </c>
       <c r="B95" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135648273</v>
       </c>
       <c r="B96" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>135648277</v>
       </c>
       <c r="B97" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135648299</v>
       </c>
       <c r="B98" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135648331</v>
       </c>
       <c r="B99" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>135648334</v>
       </c>
       <c r="B100" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>135648339</v>
       </c>
       <c r="B101" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>135648366</v>
       </c>
       <c r="B102" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>135648385</v>
       </c>
       <c r="B103" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>135648386</v>
       </c>
       <c r="B104" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>135648387</v>
       </c>
       <c r="B105" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>135648392</v>
       </c>
       <c r="B106" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>135648428</v>
       </c>
       <c r="B107" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>135648438</v>
       </c>
       <c r="B108" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>135648251</v>
       </c>
       <c r="B109" t="n">
-        <v>83411</v>
+        <v>83413</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135648244</v>
       </c>
       <c r="B111" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>135648248</v>
       </c>
       <c r="B112" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>135648254</v>
       </c>
       <c r="B113" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>135648266</v>
       </c>
       <c r="B114" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>135648279</v>
       </c>
       <c r="B115" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>135648280</v>
       </c>
       <c r="B116" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135648327</v>
       </c>
       <c r="B117" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>135648388</v>
       </c>
       <c r="B118" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>135648267</v>
       </c>
       <c r="B121" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135648376</v>
       </c>
       <c r="B122" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>135648380</v>
       </c>
       <c r="B123" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>135648383</v>
       </c>
       <c r="B124" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>135648296</v>
       </c>
       <c r="B129" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>135648349</v>
       </c>
       <c r="B130" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>135648259</v>
       </c>
       <c r="B131" t="n">
-        <v>79697</v>
+        <v>79699</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>135648294</v>
       </c>
       <c r="B132" t="n">
-        <v>79697</v>
+        <v>79699</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>135648307</v>
       </c>
       <c r="B133" t="n">
-        <v>79697</v>
+        <v>79699</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>135648395</v>
       </c>
       <c r="B134" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>135648293</v>
       </c>
       <c r="B136" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>135648318</v>
       </c>
       <c r="B137" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>135648422</v>
       </c>
       <c r="B138" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>135648243</v>
       </c>
       <c r="B139" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>135648257</v>
       </c>
       <c r="B140" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>135648262</v>
       </c>
       <c r="B141" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>135648269</v>
       </c>
       <c r="B142" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>135648300</v>
       </c>
       <c r="B143" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>135648301</v>
       </c>
       <c r="B144" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>135648309</v>
       </c>
       <c r="B145" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>135648313</v>
       </c>
       <c r="B146" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>135648316</v>
       </c>
       <c r="B147" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>135648319</v>
       </c>
       <c r="B148" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>135648321</v>
       </c>
       <c r="B149" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>135648322</v>
       </c>
       <c r="B150" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>135648323</v>
       </c>
       <c r="B151" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>135648325</v>
       </c>
       <c r="B152" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>135648326</v>
       </c>
       <c r="B153" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>135648328</v>
       </c>
       <c r="B154" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>135648332</v>
       </c>
       <c r="B155" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>135648333</v>
       </c>
       <c r="B156" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>135648336</v>
       </c>
       <c r="B157" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>135648343</v>
       </c>
       <c r="B158" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>135648358</v>
       </c>
       <c r="B159" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>135648359</v>
       </c>
       <c r="B160" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>135648362</v>
       </c>
       <c r="B161" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>135648364</v>
       </c>
       <c r="B162" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>135648371</v>
       </c>
       <c r="B163" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>135648377</v>
       </c>
       <c r="B164" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>135648379</v>
       </c>
       <c r="B165" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>135648390</v>
       </c>
       <c r="B166" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>135648391</v>
       </c>
       <c r="B167" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>135648439</v>
       </c>
       <c r="B168" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>135648409</v>
       </c>
       <c r="B169" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>135648368</v>
       </c>
       <c r="B170" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>135648253</v>
       </c>
       <c r="B171" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>135648324</v>
       </c>
       <c r="B172" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>135648374</v>
       </c>
       <c r="B173" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>135648408</v>
       </c>
       <c r="B174" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>135648292</v>
       </c>
       <c r="B175" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>135648396</v>
       </c>
       <c r="B176" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>135648272</v>
       </c>
       <c r="B177" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>135648287</v>
       </c>
       <c r="B178" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>135648314</v>
       </c>
       <c r="B179" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>135648320</v>
       </c>
       <c r="B180" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>135648384</v>
       </c>
       <c r="B181" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>135648394</v>
       </c>
       <c r="B182" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>135648399</v>
       </c>
       <c r="B183" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>135648400</v>
       </c>
       <c r="B184" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>135648401</v>
       </c>
       <c r="B185" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135648404</v>
       </c>
       <c r="B186" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>135648405</v>
       </c>
       <c r="B187" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>135648407</v>
       </c>
       <c r="B188" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>135648258</v>
       </c>
       <c r="B189" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>135648295</v>
       </c>
       <c r="B190" t="n">
-        <v>80506</v>
+        <v>80508</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/S 2068-2026 artfynd.xlsx
+++ b/artfynd/S 2068-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135648264</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135648413</v>
       </c>
       <c r="B3" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135648414</v>
       </c>
       <c r="B4" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135648421</v>
       </c>
       <c r="B5" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135648430</v>
       </c>
       <c r="B6" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135648435</v>
       </c>
       <c r="B7" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>135648367</v>
       </c>
       <c r="B9" t="n">
-        <v>83415</v>
+        <v>83416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135648249</v>
       </c>
       <c r="B10" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135648369</v>
       </c>
       <c r="B11" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135648312</v>
       </c>
       <c r="B12" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135648365</v>
       </c>
       <c r="B13" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135648246</v>
       </c>
       <c r="B14" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135648255</v>
       </c>
       <c r="B15" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135648260</v>
       </c>
       <c r="B16" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135648276</v>
       </c>
       <c r="B17" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135648278</v>
       </c>
       <c r="B18" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135648281</v>
       </c>
       <c r="B19" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135648283</v>
       </c>
       <c r="B20" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135648284</v>
       </c>
       <c r="B21" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135648288</v>
       </c>
       <c r="B22" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135648298</v>
       </c>
       <c r="B23" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135648304</v>
       </c>
       <c r="B24" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135648305</v>
       </c>
       <c r="B25" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135648335</v>
       </c>
       <c r="B26" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135648338</v>
       </c>
       <c r="B27" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135648340</v>
       </c>
       <c r="B28" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135648341</v>
       </c>
       <c r="B29" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135648344</v>
       </c>
       <c r="B30" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>135648345</v>
       </c>
       <c r="B31" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>135648347</v>
       </c>
       <c r="B32" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135648348</v>
       </c>
       <c r="B33" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135648351</v>
       </c>
       <c r="B34" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135648354</v>
       </c>
       <c r="B35" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135648356</v>
       </c>
       <c r="B36" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135648357</v>
       </c>
       <c r="B37" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135648370</v>
       </c>
       <c r="B38" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>135648372</v>
       </c>
       <c r="B39" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135648398</v>
       </c>
       <c r="B40" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135648411</v>
       </c>
       <c r="B41" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135648415</v>
       </c>
       <c r="B42" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135648418</v>
       </c>
       <c r="B43" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135648419</v>
       </c>
       <c r="B44" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135648420</v>
       </c>
       <c r="B45" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>135648423</v>
       </c>
       <c r="B46" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>135648425</v>
       </c>
       <c r="B47" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135648429</v>
       </c>
       <c r="B48" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>135648432</v>
       </c>
       <c r="B49" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>135648433</v>
       </c>
       <c r="B50" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135648436</v>
       </c>
       <c r="B51" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>135648437</v>
       </c>
       <c r="B52" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>135648440</v>
       </c>
       <c r="B53" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135648342</v>
       </c>
       <c r="B54" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>135648256</v>
       </c>
       <c r="B58" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135648263</v>
       </c>
       <c r="B59" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135648275</v>
       </c>
       <c r="B60" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>135648282</v>
       </c>
       <c r="B61" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>135648285</v>
       </c>
       <c r="B62" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>135648289</v>
       </c>
       <c r="B63" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>135648311</v>
       </c>
       <c r="B64" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>135648353</v>
       </c>
       <c r="B65" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>135648373</v>
       </c>
       <c r="B66" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>135648378</v>
       </c>
       <c r="B67" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>135648389</v>
       </c>
       <c r="B68" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135648397</v>
       </c>
       <c r="B69" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>135648424</v>
       </c>
       <c r="B70" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>135648375</v>
       </c>
       <c r="B71" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>135648426</v>
       </c>
       <c r="B72" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135648427</v>
       </c>
       <c r="B73" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>135648291</v>
       </c>
       <c r="B74" t="n">
-        <v>92075</v>
+        <v>92076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>135648286</v>
       </c>
       <c r="B75" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>135648250</v>
       </c>
       <c r="B81" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135648261</v>
       </c>
       <c r="B82" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>135648382</v>
       </c>
       <c r="B83" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>135648393</v>
       </c>
       <c r="B84" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>135648431</v>
       </c>
       <c r="B85" t="n">
-        <v>92738</v>
+        <v>92739</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>135648302</v>
       </c>
       <c r="B86" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>135648337</v>
       </c>
       <c r="B87" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135648252</v>
       </c>
       <c r="B88" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>135648241</v>
       </c>
       <c r="B94" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>135648245</v>
       </c>
       <c r="B95" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135648273</v>
       </c>
       <c r="B96" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>135648277</v>
       </c>
       <c r="B97" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135648299</v>
       </c>
       <c r="B98" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135648331</v>
       </c>
       <c r="B99" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>135648334</v>
       </c>
       <c r="B100" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>135648339</v>
       </c>
       <c r="B101" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>135648366</v>
       </c>
       <c r="B102" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>135648385</v>
       </c>
       <c r="B103" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>135648386</v>
       </c>
       <c r="B104" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>135648387</v>
       </c>
       <c r="B105" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>135648392</v>
       </c>
       <c r="B106" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>135648428</v>
       </c>
       <c r="B107" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>135648438</v>
       </c>
       <c r="B108" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>135648251</v>
       </c>
       <c r="B109" t="n">
-        <v>83413</v>
+        <v>83414</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135648244</v>
       </c>
       <c r="B111" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>135648248</v>
       </c>
       <c r="B112" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>135648254</v>
       </c>
       <c r="B113" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>135648266</v>
       </c>
       <c r="B114" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>135648279</v>
       </c>
       <c r="B115" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>135648280</v>
       </c>
       <c r="B116" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135648327</v>
       </c>
       <c r="B117" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>135648388</v>
       </c>
       <c r="B118" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>135648267</v>
       </c>
       <c r="B121" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135648376</v>
       </c>
       <c r="B122" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>135648380</v>
       </c>
       <c r="B123" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>135648383</v>
       </c>
       <c r="B124" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>135648296</v>
       </c>
       <c r="B129" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>135648349</v>
       </c>
       <c r="B130" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>135648259</v>
       </c>
       <c r="B131" t="n">
-        <v>79699</v>
+        <v>79700</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>135648294</v>
       </c>
       <c r="B132" t="n">
-        <v>79699</v>
+        <v>79700</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>135648307</v>
       </c>
       <c r="B133" t="n">
-        <v>79699</v>
+        <v>79700</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>135648395</v>
       </c>
       <c r="B134" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>135648293</v>
       </c>
       <c r="B136" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>135648324</v>
       </c>
       <c r="B172" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>135648374</v>
       </c>
       <c r="B173" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>135648408</v>
       </c>
       <c r="B174" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>135648292</v>
       </c>
       <c r="B175" t="n">
-        <v>98314</v>
+        <v>98315</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>135648396</v>
       </c>
       <c r="B176" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>135648272</v>
       </c>
       <c r="B177" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>135648287</v>
       </c>
       <c r="B178" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>135648314</v>
       </c>
       <c r="B179" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>135648320</v>
       </c>
       <c r="B180" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>135648384</v>
       </c>
       <c r="B181" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>135648394</v>
       </c>
       <c r="B182" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>135648399</v>
       </c>
       <c r="B183" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>135648400</v>
       </c>
       <c r="B184" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>135648401</v>
       </c>
       <c r="B185" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135648404</v>
       </c>
       <c r="B186" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>135648405</v>
       </c>
       <c r="B187" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>135648407</v>
       </c>
       <c r="B188" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>135648258</v>
       </c>
       <c r="B189" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>135648295</v>
       </c>
       <c r="B190" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/S 2068-2026 artfynd.xlsx
+++ b/artfynd/S 2068-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135648264</v>
       </c>
       <c r="B2" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135648413</v>
       </c>
       <c r="B3" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135648414</v>
       </c>
       <c r="B4" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135648421</v>
       </c>
       <c r="B5" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135648430</v>
       </c>
       <c r="B6" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135648435</v>
       </c>
       <c r="B7" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135648312</v>
       </c>
       <c r="B12" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135648365</v>
       </c>
       <c r="B13" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135648246</v>
       </c>
       <c r="B14" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135648255</v>
       </c>
       <c r="B15" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135648260</v>
       </c>
       <c r="B16" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135648276</v>
       </c>
       <c r="B17" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135648278</v>
       </c>
       <c r="B18" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135648281</v>
       </c>
       <c r="B19" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135648283</v>
       </c>
       <c r="B20" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135648284</v>
       </c>
       <c r="B21" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135648288</v>
       </c>
       <c r="B22" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135648298</v>
       </c>
       <c r="B23" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135648304</v>
       </c>
       <c r="B24" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135648305</v>
       </c>
       <c r="B25" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135648335</v>
       </c>
       <c r="B26" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135648338</v>
       </c>
       <c r="B27" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135648340</v>
       </c>
       <c r="B28" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135648341</v>
       </c>
       <c r="B29" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135648344</v>
       </c>
       <c r="B30" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>135648345</v>
       </c>
       <c r="B31" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>135648347</v>
       </c>
       <c r="B32" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135648348</v>
       </c>
       <c r="B33" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135648351</v>
       </c>
       <c r="B34" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135648354</v>
       </c>
       <c r="B35" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135648356</v>
       </c>
       <c r="B36" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135648357</v>
       </c>
       <c r="B37" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135648370</v>
       </c>
       <c r="B38" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>135648372</v>
       </c>
       <c r="B39" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135648398</v>
       </c>
       <c r="B40" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135648411</v>
       </c>
       <c r="B41" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135648415</v>
       </c>
       <c r="B42" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135648418</v>
       </c>
       <c r="B43" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135648419</v>
       </c>
       <c r="B44" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135648420</v>
       </c>
       <c r="B45" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>135648423</v>
       </c>
       <c r="B46" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>135648425</v>
       </c>
       <c r="B47" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135648429</v>
       </c>
       <c r="B48" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>135648432</v>
       </c>
       <c r="B49" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>135648433</v>
       </c>
       <c r="B50" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135648436</v>
       </c>
       <c r="B51" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>135648437</v>
       </c>
       <c r="B52" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>135648440</v>
       </c>
       <c r="B53" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135648342</v>
       </c>
       <c r="B54" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>135648256</v>
       </c>
       <c r="B58" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135648263</v>
       </c>
       <c r="B59" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135648275</v>
       </c>
       <c r="B60" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>135648282</v>
       </c>
       <c r="B61" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>135648285</v>
       </c>
       <c r="B62" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>135648289</v>
       </c>
       <c r="B63" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>135648311</v>
       </c>
       <c r="B64" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>135648353</v>
       </c>
       <c r="B65" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>135648373</v>
       </c>
       <c r="B66" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>135648378</v>
       </c>
       <c r="B67" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>135648389</v>
       </c>
       <c r="B68" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135648397</v>
       </c>
       <c r="B69" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>135648424</v>
       </c>
       <c r="B70" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>135648375</v>
       </c>
       <c r="B71" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>135648426</v>
       </c>
       <c r="B72" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135648427</v>
       </c>
       <c r="B73" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>135648291</v>
       </c>
       <c r="B74" t="n">
-        <v>92076</v>
+        <v>92077</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>135648286</v>
       </c>
       <c r="B75" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>135648431</v>
       </c>
       <c r="B85" t="n">
-        <v>92739</v>
+        <v>92740</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>135648302</v>
       </c>
       <c r="B86" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>135648337</v>
       </c>
       <c r="B87" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135648252</v>
       </c>
       <c r="B88" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>135648324</v>
       </c>
       <c r="B172" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>135648374</v>
       </c>
       <c r="B173" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>135648408</v>
       </c>
       <c r="B174" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>135648292</v>
       </c>
       <c r="B175" t="n">
-        <v>98315</v>
+        <v>98316</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>135648396</v>
       </c>
       <c r="B176" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>135648272</v>
       </c>
       <c r="B177" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>135648287</v>
       </c>
       <c r="B178" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>135648314</v>
       </c>
       <c r="B179" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>135648320</v>
       </c>
       <c r="B180" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>135648384</v>
       </c>
       <c r="B181" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>135648394</v>
       </c>
       <c r="B182" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>135648399</v>
       </c>
       <c r="B183" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>135648400</v>
       </c>
       <c r="B184" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>135648401</v>
       </c>
       <c r="B185" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135648404</v>
       </c>
       <c r="B186" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>135648405</v>
       </c>
       <c r="B187" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>135648407</v>
       </c>
       <c r="B188" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>135648258</v>
       </c>
       <c r="B189" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/S 2068-2026 artfynd.xlsx
+++ b/artfynd/S 2068-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135648264</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135648413</v>
       </c>
       <c r="B3" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135648414</v>
       </c>
       <c r="B4" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135648421</v>
       </c>
       <c r="B5" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135648430</v>
       </c>
       <c r="B6" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135648435</v>
       </c>
       <c r="B7" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>135648367</v>
       </c>
       <c r="B9" t="n">
-        <v>83416</v>
+        <v>83417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135648249</v>
       </c>
       <c r="B10" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135648369</v>
       </c>
       <c r="B11" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135648312</v>
       </c>
       <c r="B12" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135648365</v>
       </c>
       <c r="B13" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135648246</v>
       </c>
       <c r="B14" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135648255</v>
       </c>
       <c r="B15" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135648260</v>
       </c>
       <c r="B16" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135648276</v>
       </c>
       <c r="B17" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135648278</v>
       </c>
       <c r="B18" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135648281</v>
       </c>
       <c r="B19" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135648283</v>
       </c>
       <c r="B20" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135648284</v>
       </c>
       <c r="B21" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135648288</v>
       </c>
       <c r="B22" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135648298</v>
       </c>
       <c r="B23" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135648304</v>
       </c>
       <c r="B24" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135648305</v>
       </c>
       <c r="B25" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135648335</v>
       </c>
       <c r="B26" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135648338</v>
       </c>
       <c r="B27" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135648340</v>
       </c>
       <c r="B28" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135648341</v>
       </c>
       <c r="B29" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135648344</v>
       </c>
       <c r="B30" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>135648345</v>
       </c>
       <c r="B31" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>135648347</v>
       </c>
       <c r="B32" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135648348</v>
       </c>
       <c r="B33" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135648351</v>
       </c>
       <c r="B34" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135648354</v>
       </c>
       <c r="B35" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135648356</v>
       </c>
       <c r="B36" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135648357</v>
       </c>
       <c r="B37" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135648370</v>
       </c>
       <c r="B38" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>135648372</v>
       </c>
       <c r="B39" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135648398</v>
       </c>
       <c r="B40" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135648411</v>
       </c>
       <c r="B41" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135648415</v>
       </c>
       <c r="B42" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135648418</v>
       </c>
       <c r="B43" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135648419</v>
       </c>
       <c r="B44" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135648420</v>
       </c>
       <c r="B45" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>135648423</v>
       </c>
       <c r="B46" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>135648425</v>
       </c>
       <c r="B47" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135648429</v>
       </c>
       <c r="B48" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>135648432</v>
       </c>
       <c r="B49" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>135648433</v>
       </c>
       <c r="B50" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135648436</v>
       </c>
       <c r="B51" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>135648437</v>
       </c>
       <c r="B52" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>135648440</v>
       </c>
       <c r="B53" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135648342</v>
       </c>
       <c r="B54" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>135648256</v>
       </c>
       <c r="B58" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135648263</v>
       </c>
       <c r="B59" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135648275</v>
       </c>
       <c r="B60" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>135648282</v>
       </c>
       <c r="B61" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>135648285</v>
       </c>
       <c r="B62" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>135648289</v>
       </c>
       <c r="B63" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>135648311</v>
       </c>
       <c r="B64" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>135648353</v>
       </c>
       <c r="B65" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>135648373</v>
       </c>
       <c r="B66" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>135648378</v>
       </c>
       <c r="B67" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>135648389</v>
       </c>
       <c r="B68" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135648397</v>
       </c>
       <c r="B69" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>135648424</v>
       </c>
       <c r="B70" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>135648375</v>
       </c>
       <c r="B71" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>135648426</v>
       </c>
       <c r="B72" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135648427</v>
       </c>
       <c r="B73" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>135648291</v>
       </c>
       <c r="B74" t="n">
-        <v>92077</v>
+        <v>92078</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>135648286</v>
       </c>
       <c r="B75" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>135648250</v>
       </c>
       <c r="B81" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135648261</v>
       </c>
       <c r="B82" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>135648382</v>
       </c>
       <c r="B83" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>135648393</v>
       </c>
       <c r="B84" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>135648431</v>
       </c>
       <c r="B85" t="n">
-        <v>92740</v>
+        <v>92741</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>135648302</v>
       </c>
       <c r="B86" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>135648337</v>
       </c>
       <c r="B87" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135648252</v>
       </c>
       <c r="B88" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>135648241</v>
       </c>
       <c r="B94" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>135648245</v>
       </c>
       <c r="B95" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135648273</v>
       </c>
       <c r="B96" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>135648277</v>
       </c>
       <c r="B97" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135648299</v>
       </c>
       <c r="B98" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135648331</v>
       </c>
       <c r="B99" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>135648334</v>
       </c>
       <c r="B100" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>135648339</v>
       </c>
       <c r="B101" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>135648366</v>
       </c>
       <c r="B102" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>135648385</v>
       </c>
       <c r="B103" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>135648386</v>
       </c>
       <c r="B104" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>135648387</v>
       </c>
       <c r="B105" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>135648392</v>
       </c>
       <c r="B106" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>135648428</v>
       </c>
       <c r="B107" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>135648438</v>
       </c>
       <c r="B108" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>135648251</v>
       </c>
       <c r="B109" t="n">
-        <v>83414</v>
+        <v>83415</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135648244</v>
       </c>
       <c r="B111" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>135648248</v>
       </c>
       <c r="B112" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>135648254</v>
       </c>
       <c r="B113" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>135648266</v>
       </c>
       <c r="B114" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>135648279</v>
       </c>
       <c r="B115" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>135648280</v>
       </c>
       <c r="B116" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135648327</v>
       </c>
       <c r="B117" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>135648388</v>
       </c>
       <c r="B118" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>135648267</v>
       </c>
       <c r="B121" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135648376</v>
       </c>
       <c r="B122" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>135648380</v>
       </c>
       <c r="B123" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>135648383</v>
       </c>
       <c r="B124" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>135648296</v>
       </c>
       <c r="B129" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>135648349</v>
       </c>
       <c r="B130" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>135648259</v>
       </c>
       <c r="B131" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>135648294</v>
       </c>
       <c r="B132" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>135648307</v>
       </c>
       <c r="B133" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>135648395</v>
       </c>
       <c r="B134" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>135648293</v>
       </c>
       <c r="B136" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>135648318</v>
       </c>
       <c r="B137" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>135648422</v>
       </c>
       <c r="B138" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>135648243</v>
       </c>
       <c r="B139" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>135648257</v>
       </c>
       <c r="B140" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>135648262</v>
       </c>
       <c r="B141" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>135648269</v>
       </c>
       <c r="B142" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>135648300</v>
       </c>
       <c r="B143" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>135648301</v>
       </c>
       <c r="B144" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>135648309</v>
       </c>
       <c r="B145" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>135648313</v>
       </c>
       <c r="B146" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>135648316</v>
       </c>
       <c r="B147" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>135648319</v>
       </c>
       <c r="B148" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>135648321</v>
       </c>
       <c r="B149" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>135648322</v>
       </c>
       <c r="B150" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>135648323</v>
       </c>
       <c r="B151" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>135648325</v>
       </c>
       <c r="B152" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>135648326</v>
       </c>
       <c r="B153" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>135648328</v>
       </c>
       <c r="B154" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>135648332</v>
       </c>
       <c r="B155" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>135648333</v>
       </c>
       <c r="B156" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>135648336</v>
       </c>
       <c r="B157" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>135648343</v>
       </c>
       <c r="B158" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>135648358</v>
       </c>
       <c r="B159" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>135648359</v>
       </c>
       <c r="B160" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>135648362</v>
       </c>
       <c r="B161" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>135648364</v>
       </c>
       <c r="B162" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>135648371</v>
       </c>
       <c r="B163" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>135648377</v>
       </c>
       <c r="B164" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>135648379</v>
       </c>
       <c r="B165" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>135648390</v>
       </c>
       <c r="B166" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>135648391</v>
       </c>
       <c r="B167" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>135648439</v>
       </c>
       <c r="B168" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>135648409</v>
       </c>
       <c r="B169" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>135648368</v>
       </c>
       <c r="B170" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>135648253</v>
       </c>
       <c r="B171" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>135648324</v>
       </c>
       <c r="B172" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>135648374</v>
       </c>
       <c r="B173" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>135648408</v>
       </c>
       <c r="B174" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>135648292</v>
       </c>
       <c r="B175" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>135648396</v>
       </c>
       <c r="B176" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>135648272</v>
       </c>
       <c r="B177" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>135648287</v>
       </c>
       <c r="B178" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>135648314</v>
       </c>
       <c r="B179" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>135648320</v>
       </c>
       <c r="B180" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>135648384</v>
       </c>
       <c r="B181" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>135648394</v>
       </c>
       <c r="B182" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>135648399</v>
       </c>
       <c r="B183" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>135648400</v>
       </c>
       <c r="B184" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>135648401</v>
       </c>
       <c r="B185" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135648404</v>
       </c>
       <c r="B186" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>135648405</v>
       </c>
       <c r="B187" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>135648407</v>
       </c>
       <c r="B188" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>135648258</v>
       </c>
       <c r="B189" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>135648295</v>
       </c>
       <c r="B190" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/S 2068-2026 artfynd.xlsx
+++ b/artfynd/S 2068-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135648264</v>
       </c>
       <c r="B2" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135648413</v>
       </c>
       <c r="B3" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135648414</v>
       </c>
       <c r="B4" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135648421</v>
       </c>
       <c r="B5" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135648430</v>
       </c>
       <c r="B6" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135648435</v>
       </c>
       <c r="B7" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>135648367</v>
       </c>
       <c r="B9" t="n">
-        <v>83417</v>
+        <v>83421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135648249</v>
       </c>
       <c r="B10" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135648369</v>
       </c>
       <c r="B11" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135648312</v>
       </c>
       <c r="B12" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135648365</v>
       </c>
       <c r="B13" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135648246</v>
       </c>
       <c r="B14" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135648255</v>
       </c>
       <c r="B15" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135648260</v>
       </c>
       <c r="B16" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135648276</v>
       </c>
       <c r="B17" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135648278</v>
       </c>
       <c r="B18" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135648281</v>
       </c>
       <c r="B19" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>135648283</v>
       </c>
       <c r="B20" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135648284</v>
       </c>
       <c r="B21" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>135648288</v>
       </c>
       <c r="B22" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>135648298</v>
       </c>
       <c r="B23" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>135648304</v>
       </c>
       <c r="B24" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>135648305</v>
       </c>
       <c r="B25" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>135648335</v>
       </c>
       <c r="B26" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>135648338</v>
       </c>
       <c r="B27" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>135648340</v>
       </c>
       <c r="B28" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>135648341</v>
       </c>
       <c r="B29" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>135648344</v>
       </c>
       <c r="B30" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>135648345</v>
       </c>
       <c r="B31" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>135648347</v>
       </c>
       <c r="B32" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>135648348</v>
       </c>
       <c r="B33" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135648351</v>
       </c>
       <c r="B34" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>135648354</v>
       </c>
       <c r="B35" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>135648356</v>
       </c>
       <c r="B36" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>135648357</v>
       </c>
       <c r="B37" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>135648370</v>
       </c>
       <c r="B38" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>135648372</v>
       </c>
       <c r="B39" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135648398</v>
       </c>
       <c r="B40" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135648411</v>
       </c>
       <c r="B41" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135648415</v>
       </c>
       <c r="B42" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135648418</v>
       </c>
       <c r="B43" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135648419</v>
       </c>
       <c r="B44" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>135648420</v>
       </c>
       <c r="B45" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>135648423</v>
       </c>
       <c r="B46" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>135648425</v>
       </c>
       <c r="B47" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>135648429</v>
       </c>
       <c r="B48" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
         <v>135648432</v>
       </c>
       <c r="B49" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>135648433</v>
       </c>
       <c r="B50" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>135648436</v>
       </c>
       <c r="B51" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>135648437</v>
       </c>
       <c r="B52" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>135648440</v>
       </c>
       <c r="B53" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>135648342</v>
       </c>
       <c r="B54" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>135648256</v>
       </c>
       <c r="B58" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>135648263</v>
       </c>
       <c r="B59" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>135648275</v>
       </c>
       <c r="B60" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>135648282</v>
       </c>
       <c r="B61" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>135648285</v>
       </c>
       <c r="B62" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>135648289</v>
       </c>
       <c r="B63" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>135648311</v>
       </c>
       <c r="B64" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>135648353</v>
       </c>
       <c r="B65" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>135648373</v>
       </c>
       <c r="B66" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>135648378</v>
       </c>
       <c r="B67" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>135648389</v>
       </c>
       <c r="B68" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135648397</v>
       </c>
       <c r="B69" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>135648424</v>
       </c>
       <c r="B70" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>135648375</v>
       </c>
       <c r="B71" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>135648426</v>
       </c>
       <c r="B72" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>135648427</v>
       </c>
       <c r="B73" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>135648291</v>
       </c>
       <c r="B74" t="n">
-        <v>92078</v>
+        <v>92084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>135648286</v>
       </c>
       <c r="B75" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>135648250</v>
       </c>
       <c r="B81" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9680,7 +9680,7 @@
         <v>135648261</v>
       </c>
       <c r="B82" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>135648382</v>
       </c>
       <c r="B83" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>135648393</v>
       </c>
       <c r="B84" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>135648431</v>
       </c>
       <c r="B85" t="n">
-        <v>92741</v>
+        <v>92747</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>135648302</v>
       </c>
       <c r="B86" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>135648337</v>
       </c>
       <c r="B87" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>135648252</v>
       </c>
       <c r="B88" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>135648241</v>
       </c>
       <c r="B94" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>135648245</v>
       </c>
       <c r="B95" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135648273</v>
       </c>
       <c r="B96" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>135648277</v>
       </c>
       <c r="B97" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>135648299</v>
       </c>
       <c r="B98" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>135648331</v>
       </c>
       <c r="B99" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>135648334</v>
       </c>
       <c r="B100" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>135648339</v>
       </c>
       <c r="B101" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>135648366</v>
       </c>
       <c r="B102" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         <v>135648385</v>
       </c>
       <c r="B103" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>135648386</v>
       </c>
       <c r="B104" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>135648387</v>
       </c>
       <c r="B105" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>135648392</v>
       </c>
       <c r="B106" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>135648428</v>
       </c>
       <c r="B107" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>135648438</v>
       </c>
       <c r="B108" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>135648251</v>
       </c>
       <c r="B109" t="n">
-        <v>83415</v>
+        <v>83419</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>135648244</v>
       </c>
       <c r="B111" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>135648248</v>
       </c>
       <c r="B112" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>135648254</v>
       </c>
       <c r="B113" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>135648266</v>
       </c>
       <c r="B114" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>135648279</v>
       </c>
       <c r="B115" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>135648280</v>
       </c>
       <c r="B116" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>135648327</v>
       </c>
       <c r="B117" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>135648388</v>
       </c>
       <c r="B118" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>135648267</v>
       </c>
       <c r="B121" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135648376</v>
       </c>
       <c r="B122" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>135648380</v>
       </c>
       <c r="B123" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>135648383</v>
       </c>
       <c r="B124" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>135648296</v>
       </c>
       <c r="B129" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>135648349</v>
       </c>
       <c r="B130" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>135648259</v>
       </c>
       <c r="B131" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>135648294</v>
       </c>
       <c r="B132" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>135648307</v>
       </c>
       <c r="B133" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>135648395</v>
       </c>
       <c r="B134" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>135648293</v>
       </c>
       <c r="B136" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>135648318</v>
       </c>
       <c r="B137" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>135648422</v>
       </c>
       <c r="B138" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>135648243</v>
       </c>
       <c r="B139" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>135648257</v>
       </c>
       <c r="B140" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>135648262</v>
       </c>
       <c r="B141" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>135648269</v>
       </c>
       <c r="B142" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>135648300</v>
       </c>
       <c r="B143" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>135648301</v>
       </c>
       <c r="B144" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>135648309</v>
       </c>
       <c r="B145" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>135648313</v>
       </c>
       <c r="B146" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>135648316</v>
       </c>
       <c r="B147" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>135648319</v>
       </c>
       <c r="B148" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>135648321</v>
       </c>
       <c r="B149" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>135648322</v>
       </c>
       <c r="B150" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>135648323</v>
       </c>
       <c r="B151" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>135648325</v>
       </c>
       <c r="B152" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>135648326</v>
       </c>
       <c r="B153" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>135648328</v>
       </c>
       <c r="B154" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>135648332</v>
       </c>
       <c r="B155" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>135648333</v>
       </c>
       <c r="B156" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>135648336</v>
       </c>
       <c r="B157" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>135648343</v>
       </c>
       <c r="B158" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>135648358</v>
       </c>
       <c r="B159" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18761,7 +18761,7 @@
         <v>135648359</v>
       </c>
       <c r="B160" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>135648362</v>
       </c>
       <c r="B161" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         <v>135648364</v>
       </c>
       <c r="B162" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>135648371</v>
       </c>
       <c r="B163" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>135648377</v>
       </c>
       <c r="B164" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>135648379</v>
       </c>
       <c r="B165" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>135648390</v>
       </c>
       <c r="B166" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>135648391</v>
       </c>
       <c r="B167" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>135648439</v>
       </c>
       <c r="B168" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>135648409</v>
       </c>
       <c r="B169" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20013,7 +20013,7 @@
         <v>135648368</v>
       </c>
       <c r="B170" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>135648253</v>
       </c>
       <c r="B171" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>135648324</v>
       </c>
       <c r="B172" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>135648374</v>
       </c>
       <c r="B173" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>135648408</v>
       </c>
       <c r="B174" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>135648292</v>
       </c>
       <c r="B175" t="n">
-        <v>98317</v>
+        <v>98323</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>135648396</v>
       </c>
       <c r="B176" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>135648272</v>
       </c>
       <c r="B177" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>135648287</v>
       </c>
       <c r="B178" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>135648314</v>
       </c>
       <c r="B179" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>135648320</v>
       </c>
       <c r="B180" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>135648384</v>
       </c>
       <c r="B181" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>135648394</v>
       </c>
       <c r="B182" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>135648399</v>
       </c>
       <c r="B183" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>135648400</v>
       </c>
       <c r="B184" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>135648401</v>
       </c>
       <c r="B185" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>135648404</v>
       </c>
       <c r="B186" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>135648405</v>
       </c>
       <c r="B187" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>135648407</v>
       </c>
       <c r="B188" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>135648258</v>
       </c>
       <c r="B189" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>135648295</v>
       </c>
       <c r="B190" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/S 2068-2026 artfynd.xlsx
+++ b/artfynd/S 2068-2026 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>135648367</v>
       </c>
       <c r="B9" t="n">
-        <v>83421</v>
+        <v>83422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
